--- a/2018/Mount1/Mount1_members_final.xlsx
+++ b/2018/Mount1/Mount1_members_final.xlsx
@@ -796,7 +796,7 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>مستقل</t>
         </is>
       </c>
     </row>
@@ -823,7 +823,7 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>مستقل</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>مستقل</t>
         </is>
       </c>
     </row>
